--- a/artfynd/A 153-2025 artfynd.xlsx
+++ b/artfynd/A 153-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">

--- a/artfynd/A 153-2025 artfynd.xlsx
+++ b/artfynd/A 153-2025 artfynd.xlsx
@@ -811,7 +811,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">

--- a/artfynd/A 153-2025 artfynd.xlsx
+++ b/artfynd/A 153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>81011773</v>
       </c>
       <c r="B2" t="n">
-        <v>56990</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>684553.089196017</v>
+        <v>684553</v>
       </c>
       <c r="R2" t="n">
-        <v>6598171.836921304</v>
+        <v>6598172</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,19 +755,9 @@
           <t>2019-11-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-11-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,37 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87922107</v>
+        <v>87922020</v>
       </c>
       <c r="B3" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205976</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -851,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>684648.1353267505</v>
+        <v>684214</v>
       </c>
       <c r="R3" t="n">
-        <v>6598011.129000365</v>
+        <v>6598461</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -881,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,37 +893,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87922106</v>
+        <v>87922021</v>
       </c>
       <c r="B4" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205976</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,7 +930,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -975,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684533.8272155026</v>
+        <v>684516</v>
       </c>
       <c r="R4" t="n">
-        <v>6598180.05097273</v>
+        <v>6598250</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1008,19 +973,9 @@
           <t>2020-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,37 +1002,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87921818</v>
+        <v>87921938</v>
       </c>
       <c r="B5" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205976</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1086,10 +1036,14 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1099,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684561.8684128716</v>
+        <v>684474</v>
       </c>
       <c r="R5" t="n">
-        <v>6598179.899867637</v>
+        <v>6598205</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1129,22 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-04-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-04-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fingal Gyllang</t>
+          <t>Björn Averhed</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1174,12 +1118,7 @@
         <v>87921983</v>
       </c>
       <c r="B6" t="n">
-        <v>56779</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684634.1232590843</v>
+        <v>684634</v>
       </c>
       <c r="R6" t="n">
-        <v>6598057.763717671</v>
+        <v>6598058</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1256,19 +1195,9 @@
           <t>2020-05-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-05-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,16 +1227,11 @@
         <v>87921805</v>
       </c>
       <c r="B7" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1351,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684590.9153091367</v>
+        <v>684591</v>
       </c>
       <c r="R7" t="n">
-        <v>6598044.958199194</v>
+        <v>6598045</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1384,19 +1308,9 @@
           <t>2020-04-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-04-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,69 +1337,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87921938</v>
+        <v>81011775</v>
       </c>
       <c r="B8" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åkers Runö, Upl</t>
+          <t>Täljö, Österåker, Österåkers golfbana, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>684473.983008436</v>
+        <v>684553</v>
       </c>
       <c r="R8" t="n">
-        <v>6598205.10145265</v>
+        <v>6598172</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,22 +1414,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,15 +1434,342 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Raul Vicente</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>87921818</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Åkers Runö, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>684562</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6598180</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-04-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-04-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Rikard Anderberg</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fingal Gyllang</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>87922106</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Åkers Runö, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>684534</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6598180</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-06-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-06-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Björn Averhed</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>87922107</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åkers Runö, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>684648</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6598011</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-05-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rikard Anderberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Björn Averhed</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 153-2025 artfynd.xlsx
+++ b/artfynd/A 153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81011773</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87922020</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87922021</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87921938</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87921983</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87921805</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1443,6 +1478,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81011775</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87921818</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1661,6 +1706,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87922106</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,8 +1820,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87922107</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>